--- a/Universidad del Valle.xlsx
+++ b/Universidad del Valle.xlsx
@@ -22,6 +22,7 @@
     <sheet name="Economía" sheetId="7" r:id="rId7"/>
     <sheet name="Gestión Emprend. e Innovación" sheetId="8" r:id="rId8"/>
     <sheet name="Administración Turística" sheetId="9" r:id="rId9"/>
+    <sheet name="Administración Pública" sheetId="10" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2467" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2673" uniqueCount="626">
   <si>
     <t>Relación materias – simuladores CompanyGame</t>
   </si>
@@ -124,7 +125,7 @@
     <t xml:space="preserve">  Comercio Exterior (9 sem), Finanzas y Banca (9 sem, 150 cr), Economía (Res. 045/2020, 9 sem),</t>
   </si>
   <si>
-    <t xml:space="preserve">  Gestión del Emprendimiento y la Innovación (8 sem, 140 cr) y Administración Turística (9 sem).</t>
+    <t xml:space="preserve">  Gestión del Emprendimiento y la Innovación (8 sem, 140 cr), Administración Turística (9 sem) y Administración Pública (Res. 004/2020, 8 sem).</t>
   </si>
   <si>
     <t>· Catálogo de simuladores tomado de companygame.com (8 categorías; ver hoja 'Catálogo CompanyGame').</t>
@@ -136,7 +137,7 @@
     <t>· Administración Turística apalanca la línea HORECA; Finanzas y Banca la línea Finanzas y Banca (Bankgame/Trading/BankCompany);</t>
   </si>
   <si>
-    <t xml:space="preserve">  Economía es muy teórica-cuantitativa (bajo encaje directo).</t>
+    <t xml:space="preserve">  Economía y Administración Pública son los más teórico-conceptuales (bajo encaje directo); Administración Pública se verificó contenido por contenido, no solo por nombre de la asignatura.</t>
   </si>
   <si>
     <t>Catálogo de simuladores CompanyGame</t>
@@ -1745,6 +1746,180 @@
   </si>
   <si>
     <t xml:space="preserve">Inter Pyme </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administración Pública  ·  Universidad del Valle (Univalle)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matemáticas I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Constitución Política de Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador jurídico-institucional (Estado, derecho público y contratación)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Doctrinas Políticas y Teorías del Estado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ciencia Política</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electiva de Estilos de Vida Saludable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentos del Lenguaje y Comunicación en Español</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matemáticas II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentos de Administración</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historia de las Transformaciones Sociales y Políticas de Colombia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Historia / Ciencia Política</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electiva Artístico y Humanista</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electiva de Formación Social y Ciudadana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economía I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensamiento Administrativo de lo Público I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de teoría de la administración pública (no aplica simulador de negocios)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundamentos de Contabilidad Financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introducción General al Derecho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economía II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matemática Financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derecho Administrativo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pensamiento Administrativo de lo Público II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contratación Estatal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jurídica / Sector Público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de contratación estatal (sin equivalente en el catálogo actual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Social y Político</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marketing Público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de marketing público y comunicación política (distinto del marketing comercial del catálogo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hacienda Pública y Finanzas Públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sociología de las Organizaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Humanidades / Sociología</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Política Económica Nacional e Internacional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Responsabilidad Social y Gestión Humana en el Sector Público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector Público / RR.HH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de responsabilidad social y gestión del talento humano en el sector público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulación e Implementación de Políticas Públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Políticas Públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de formulación e implementación de políticas públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sistemas de Gestión de Calidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector Público / Calidad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de gestión de calidad en el sector público (NTCGP 1000 / ISO 9001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planeación Estatal y Presupuesto Público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Derecho Internacional Público, Cooperación Internacional y Relaciones Internacionales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relaciones Internacionales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de relaciones internacionales y cooperación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prospectiva Territorial y Estratégica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taller de Lenguaje y Comunicación en Español para la Redacción de Textos Académicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evaluación de Políticas Públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de evaluación de políticas públicas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Innovación Social, Gobernanza y Buen Gobierno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sector Público / Innovación</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de innovación social y buen gobierno (distinto de la innovación corporativa del catálogo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Componente Científico Tecnológico en el Sector Público</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diseño y Evaluación de Proyectos Sociales</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Simulador de formulación y evaluación de proyectos (VPN/TIR), aplicado aquí a un proyecto social y no empresarial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presupuesto Público y Control Fiscal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Administración Pública</t>
   </si>
 </sst>
 </file>
@@ -2322,7 +2497,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G30"/>
+  <dimension ref="B2:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -2386,7 +2561,7 @@
         <v>47</v>
       </c>
       <c r="G7" s="7">
-        <f t="shared" ref="G7:G14" si="0">IFERROR((D7+E7)/C7,0)</f>
+        <f t="shared" ref="G7:G15" si="0">IFERROR((D7+E7)/C7,0)</f>
         <v>0.21311475409836064</v>
       </c>
     </row>
@@ -2541,53 +2716,66 @@
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="5" t="s">
+        <v>625</v>
+      </c>
+      <c r="C14" s="6">
+        <f>COUNTA('Administración Pública'!$B$3:$B$200)</f>
+        <v>50</v>
+      </c>
+      <c r="D14" s="6">
+        <f>COUNTIF('Administración Pública'!$F$3:$F$200,"Encaje perfecto")</f>
+        <v>2</v>
+      </c>
+      <c r="E14" s="6">
+        <f>COUNTIF('Administración Pública'!$F$3:$F$200,"Encaje parcial")</f>
+        <v>2</v>
+      </c>
+      <c r="F14" s="6">
+        <f>COUNTIF('Administración Pública'!$F$3:$F$200,"No encaja")</f>
+        <v>46</v>
+      </c>
+      <c r="G14" s="7">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C14" s="9">
-        <f>SUM(C7:C13)</f>
-        <v>381</v>
-      </c>
-      <c r="D14" s="9">
-        <f>SUM(D7:D13)</f>
-        <v>29</v>
-      </c>
-      <c r="E14" s="9">
-        <f>SUM(E7:E13)</f>
-        <v>41</v>
-      </c>
-      <c r="F14" s="9">
-        <f>SUM(F7:F13)</f>
-        <v>310</v>
-      </c>
-      <c r="G14" s="10">
+      <c r="C15" s="9">
+        <f>SUM(C7:C14)</f>
+        <v>431</v>
+      </c>
+      <c r="D15" s="9">
+        <f>SUM(D7:D14)</f>
+        <v>31</v>
+      </c>
+      <c r="E15" s="9">
+        <f>SUM(E7:E14)</f>
+        <v>43</v>
+      </c>
+      <c r="F15" s="9">
+        <f>SUM(F7:F14)</f>
+        <v>356</v>
+      </c>
+      <c r="G15" s="10">
         <f t="shared" si="0"/>
-        <v>0.18372703412073491</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
+        <v>0.1716937354988399</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="12" t="s">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C18" s="28" t="s">
         <v>18</v>
-      </c>
-      <c r="D17" s="29"/>
-      <c r="E17" s="29"/>
-      <c r="F17" s="29"/>
-      <c r="G17" s="29"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="28" t="s">
-        <v>19</v>
       </c>
       <c r="D18" s="29"/>
       <c r="E18" s="29"/>
@@ -2595,64 +2783,76 @@
       <c r="G18" s="29"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="14" t="s">
-        <v>20</v>
+      <c r="B19" s="13" t="s">
+        <v>6</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="29"/>
       <c r="G19" s="29"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="11" t="s">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="C20" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="11" t="s">
         <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="15" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B31" s="15" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2662,6 +2862,1247 @@
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="C17:G17"/>
   </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+  <dimension ref="A1:H52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="58" customWidth="1"/>
+    <col min="3" max="3" width="26" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
+    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="7" max="7" width="46" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="20">
+        <v>1</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>569</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F3" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H3" s="21"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="20">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>570</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="H4" s="21"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="20">
+        <v>1</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>572</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>573</v>
+      </c>
+      <c r="D5" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="20">
+        <v>1</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F6" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H6" s="21"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="20">
+        <v>1</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>574</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>168</v>
+      </c>
+      <c r="D7" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F7" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="H7" s="21"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="20">
+        <v>1</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>575</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="21"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="20">
+        <v>1</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D9" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" s="21"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="20">
+        <v>2</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>576</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>145</v>
+      </c>
+      <c r="H10" s="21"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="20">
+        <v>2</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="20">
+        <v>2</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>579</v>
+      </c>
+      <c r="D12" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="20">
+        <v>2</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>580</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D13" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="H13" s="21"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="20">
+        <v>2</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D14" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F14" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G14" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="H14" s="21"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="20">
+        <v>2</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>582</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F15" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H15" s="21"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="20">
+        <v>2</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F16" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H16" s="21"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="20">
+        <v>3</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D17" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F17" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H17" s="21"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="20">
+        <v>3</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D18" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F18" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="H18" s="21"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="20">
+        <v>3</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>585</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>156</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="20">
+        <v>3</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>586</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D20" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E20" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="H20" s="21"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="20">
+        <v>3</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>587</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H21" s="21"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="20">
+        <v>3</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H22" s="21"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="20">
+        <v>4</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F23" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="H23" s="21"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="20">
+        <v>4</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>588</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="G24" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="21"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="20">
+        <v>4</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="H25" s="21"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="20">
+        <v>4</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>590</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F26" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G26" s="21" t="s">
+        <v>584</v>
+      </c>
+      <c r="H26" s="21"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="20">
+        <v>4</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>581</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F27" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="H27" s="21"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="20">
+        <v>4</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F28" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="H28" s="21"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="20">
+        <v>5</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>591</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="D29" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" s="21" t="s">
+        <v>593</v>
+      </c>
+      <c r="H29" s="21"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="20">
+        <v>5</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>594</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="D30" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F30" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>596</v>
+      </c>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="20">
+        <v>5</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>597</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D31" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F31" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="H31" s="21"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="20">
+        <v>5</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>598</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>599</v>
+      </c>
+      <c r="D32" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E32" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="20">
+        <v>5</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" s="21"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="20">
+        <v>5</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>601</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>602</v>
+      </c>
+      <c r="D34" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E34" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="21" t="s">
+        <v>603</v>
+      </c>
+      <c r="H34" s="21"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="20">
+        <v>5</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D35" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H35" s="21"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="20">
+        <v>6</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>604</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="D36" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="21" t="s">
+        <v>606</v>
+      </c>
+      <c r="H36" s="21"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="20">
+        <v>6</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>607</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>608</v>
+      </c>
+      <c r="D37" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E37" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F37" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="21" t="s">
+        <v>609</v>
+      </c>
+      <c r="H37" s="21"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="20">
+        <v>6</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>610</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D38" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F38" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="H38" s="21"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="20">
+        <v>6</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>611</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>612</v>
+      </c>
+      <c r="D39" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G39" s="21" t="s">
+        <v>613</v>
+      </c>
+      <c r="H39" s="21"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="20">
+        <v>6</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>614</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="D40" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F40" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G40" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="H40" s="21"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="20">
+        <v>6</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>615</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E41" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G41" s="21" t="s">
+        <v>166</v>
+      </c>
+      <c r="H41" s="21"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="20">
+        <v>6</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D42" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F42" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G42" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H42" s="21"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="20">
+        <v>7</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>616</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>605</v>
+      </c>
+      <c r="D43" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E43" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F43" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" s="21" t="s">
+        <v>617</v>
+      </c>
+      <c r="H43" s="21"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="20">
+        <v>7</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>618</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>619</v>
+      </c>
+      <c r="D44" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E44" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F44" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G44" s="21" t="s">
+        <v>620</v>
+      </c>
+      <c r="H44" s="21"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="20">
+        <v>7</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>402</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D45" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F45" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G45" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="H45" s="21"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="20">
+        <v>7</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>621</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E46" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F46" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G46" s="21" t="s">
+        <v>154</v>
+      </c>
+      <c r="H46" s="21"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="20">
+        <v>7</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>400</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="D47" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E47" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F47" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G47" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="H47" s="21"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="20">
+        <v>7</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>622</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="D48" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="E48" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="G48" s="21" t="s">
+        <v>623</v>
+      </c>
+      <c r="H48" s="21"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="20">
+        <v>7</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>255</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D49" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E49" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F49" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G49" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H49" s="21"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="20">
+        <v>8</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>624</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="D50" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E50" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F50" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G50" s="21" t="s">
+        <v>279</v>
+      </c>
+      <c r="H50" s="21"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="20">
+        <v>8</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>368</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>257</v>
+      </c>
+      <c r="D51" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E51" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G51" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="H51" s="21"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="20">
+        <v>8</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>259</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>243</v>
+      </c>
+      <c r="D52" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E52" s="20" t="s">
+        <v>141</v>
+      </c>
+      <c r="F52" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="G52" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="H52" s="21"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
